--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ense\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73EFC5EE-B896-4F7F-9BE3-E0DAA1D3C9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E7788E-42C4-436F-A635-D8887196BD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F11" s="21"/>
       <c r="G11" s="20" t="s">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B25" s="10">
         <f>COUNTIF(Leyla!A9:G23, "Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="27"/>

--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ense\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E7788E-42C4-436F-A635-D8887196BD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9579F7-8553-43FF-9F9B-6AF356EE2450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3768" yWindow="3528" windowWidth="17280" windowHeight="10152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leyla" sheetId="1" r:id="rId1"/>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="F11" s="21"/>
       <c r="G11" s="20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B25" s="10">
         <f>COUNTIF(Leyla!A9:G23, "Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="27"/>

--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ense\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9579F7-8553-43FF-9F9B-6AF356EE2450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614E1047-154F-4867-9E29-0977D574A2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3768" yWindow="3528" windowWidth="17280" windowHeight="10152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1176,7 +1176,7 @@
       <c r="A14" s="20"/>
       <c r="B14" s="21"/>
       <c r="C14" s="20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20" t="s">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B25" s="10">
         <f>COUNTIF(Leyla!A9:G23, "Done")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="27"/>

--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ense\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614E1047-154F-4867-9E29-0977D574A2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F536FE-CE61-485B-8B4E-F2D45DF55393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3768" yWindow="3528" windowWidth="17280" windowHeight="10152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="20" t="s">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B25" s="10">
         <f>COUNTIF(Leyla!A9:G23, "Done")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="27"/>

--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ense\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F536FE-CE61-485B-8B4E-F2D45DF55393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DD1F86-1FB4-454C-B121-F4486B59DE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3768" yWindow="3528" windowWidth="17280" windowHeight="10152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leyla" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="64">
   <si>
     <t>Private Classes</t>
   </si>
@@ -215,6 +215,9 @@
   </si>
   <si>
     <t>Enes</t>
+  </si>
+  <si>
+    <t>postpone</t>
   </si>
 </sst>
 </file>
@@ -1184,7 +1187,7 @@
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="20" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1221,7 +1224,7 @@
       <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="20" t="s">
@@ -1319,7 +1322,7 @@
       </c>
       <c r="B25" s="10">
         <f>COUNTIF(Leyla!A9:G23, "Done")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="27"/>
@@ -1333,7 +1336,7 @@
       </c>
       <c r="B26" s="10">
         <f>COUNTIF(Leyla!A9:G23, "postpone")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="27"/>
